--- a/data/新能源汽车行业销量数据.xlsx
+++ b/data/新能源汽车行业销量数据.xlsx
@@ -7,10 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="厂商月度销量排行" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="整体市场月度销量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="细分市场级别销量" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="燃料类型销量" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="整体市场_销量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="整体市场_产量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="燃料类型_整体市场" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="燃料类型_轿车" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="燃料类型_SUV" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="燃料类型_MPV" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="细分市场_轿车" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="细分市场_SUV" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="细分市场_MPV" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="厂商月度排行" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="国别品牌销量" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="盖世品牌排行" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8家车企年度销量(万辆)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8家车企新能源渗透率(%)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8家车企季度销量(万辆)" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8家车企季度同比增速(%)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赛力斯vs长安核心对比" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +429,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2025年</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026年</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>209.2576</v>
+      </c>
+      <c r="C2" t="n">
+        <v>200.364</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>173.6659</v>
+      </c>
+      <c r="C3" t="n">
+        <v>136.9741</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>248.5014</v>
+      </c>
+      <c r="C4" t="n">
+        <v>236.4929</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>223.3138</v>
+      </c>
+      <c r="C5" t="n">
+        <v>219.3199</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>227.9242</v>
+      </c>
+      <c r="C6" t="n">
+        <v>221.3854</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>240.0137</v>
+      </c>
+      <c r="C7" t="n">
+        <v>233.6703</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>225.567</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>245.4123</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>284.6384</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>294.9257</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>310.5971</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>282.8679</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -564,6 +752,3351 @@
       </c>
       <c r="C11" t="n">
         <v>7.3396</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>其他欧系</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>德系</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>日系</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>法系</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>美系</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>自主</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>韩系</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>自主占比(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-7月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-8月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>69.59999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-9月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>71.40000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-1月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-2月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>70.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-3月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>67.59999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-4月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-5月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-6月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>75.59999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>厂商</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2021-9</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>9月同比</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>9月环比</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2021-1到9</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2020-1到9</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2019-1到9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>上汽大众</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>125019</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-28.56%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-85.3%</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>850437</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1031387</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1392306</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>上汽通用</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>124032</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-86.25%</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>901911</v>
+      </c>
+      <c r="F3" t="n">
+        <v>656907</v>
+      </c>
+      <c r="G3" t="n">
+        <v>846232</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>上汽通用五菱</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>110422</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.28%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-83.35%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>663108</v>
+      </c>
+      <c r="F4" t="n">
+        <v>460389</v>
+      </c>
+      <c r="G4" t="n">
+        <v>649480</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>吉利汽车</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>104279</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-19.05%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-88.83%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>933891</v>
+      </c>
+      <c r="F5" t="n">
+        <v>886699</v>
+      </c>
+      <c r="G5" t="n">
+        <v>964323</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>一汽大众</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>95110</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-57.62%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-92.16%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1212740</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1430131</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1395356</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>长安汽车</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>89556</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-12.11%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-90.28%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>921038</v>
+      </c>
+      <c r="F7" t="n">
+        <v>660293</v>
+      </c>
+      <c r="G7" t="n">
+        <v>549759</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>上汽乘用车</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>82973</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>27.92%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-83.91%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>515744</v>
+      </c>
+      <c r="F8" t="n">
+        <v>423936</v>
+      </c>
+      <c r="G8" t="n">
+        <v>488280</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>长城汽车</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>80014</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-15.71%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-88.85%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>717319</v>
+      </c>
+      <c r="F9" t="n">
+        <v>520339</v>
+      </c>
+      <c r="G9" t="n">
+        <v>625843</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>东风日产</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>79819</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-38.14%</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-89.73%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>777381</v>
+      </c>
+      <c r="F10" t="n">
+        <v>816870</v>
+      </c>
+      <c r="G10" t="n">
+        <v>924648</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>比亚迪汽车</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>79447</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>92.13%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-82.32%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>449436</v>
+      </c>
+      <c r="F11" t="n">
+        <v>264778</v>
+      </c>
+      <c r="G11" t="n">
+        <v>331183</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>广汽本田</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>71773</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-17.68%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-86.87%</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>546456</v>
+      </c>
+      <c r="F12" t="n">
+        <v>542402</v>
+      </c>
+      <c r="G12" t="n">
+        <v>568060</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>奇瑞汽车</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>66706</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>56.8%</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-88.2%</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>565142</v>
+      </c>
+      <c r="F13" t="n">
+        <v>266045</v>
+      </c>
+      <c r="G13" t="n">
+        <v>306708</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>东风本田</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>65423</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-31.14%</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-87.8%</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>536035</v>
+      </c>
+      <c r="F14" t="n">
+        <v>553302</v>
+      </c>
+      <c r="G14" t="n">
+        <v>575859</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>特斯拉汽车</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>56006</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>394.36%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-81.02%</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>295006</v>
+      </c>
+      <c r="F15" t="n">
+        <v>77898</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>华晨宝马</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>51557</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-8.47%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-89.78%</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>504335</v>
+      </c>
+      <c r="F16" t="n">
+        <v>450064</v>
+      </c>
+      <c r="G16" t="n">
+        <v>397498</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>广汽丰田</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>48300</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-40.37%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-91.72%</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>583477</v>
+      </c>
+      <c r="F17" t="n">
+        <v>543449</v>
+      </c>
+      <c r="G17" t="n">
+        <v>496224</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>一汽丰田</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>45180</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-46.53%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-92.32%</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>588236</v>
+      </c>
+      <c r="F18" t="n">
+        <v>561116</v>
+      </c>
+      <c r="G18" t="n">
+        <v>530224</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>长安福特</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>32022</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15.48%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-84.86%</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>211488</v>
+      </c>
+      <c r="F19" t="n">
+        <v>163719</v>
+      </c>
+      <c r="G19" t="n">
+        <v>128224</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>北京奔驰</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>27520</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-54.34%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-93.21%</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>405389</v>
+      </c>
+      <c r="F20" t="n">
+        <v>443813</v>
+      </c>
+      <c r="G20" t="n">
+        <v>398437</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>广汽乘用车</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>22930</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-26.32%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-89.63%</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221166</v>
+      </c>
+      <c r="F21" t="n">
+        <v>198184</v>
+      </c>
+      <c r="G21" t="n">
+        <v>263287</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>一汽红旗</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>20294</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-5.69%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-89.9%</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>200998</v>
+      </c>
+      <c r="F22" t="n">
+        <v>123481</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60680</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>北京现代</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>19390</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-51.76%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-92.58%</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>261175</v>
+      </c>
+      <c r="F23" t="n">
+        <v>302816</v>
+      </c>
+      <c r="G23" t="n">
+        <v>450812</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>长安马自达</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>17357</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16.52%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-81.37%</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>93148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>94332</v>
+      </c>
+      <c r="G24" t="n">
+        <v>95845</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>东风乘用车</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>16467</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>159.45%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-78.43%</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>76342</v>
+      </c>
+      <c r="F25" t="n">
+        <v>45376</v>
+      </c>
+      <c r="G25" t="n">
+        <v>46933</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>东风柳汽</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14463</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>59.37%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-84.19%</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>91497</v>
+      </c>
+      <c r="F26" t="n">
+        <v>63548</v>
+      </c>
+      <c r="G26" t="n">
+        <v>82855</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>14054</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>32.99%</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-87.85%</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>115689</v>
+      </c>
+      <c r="F27" t="n">
+        <v>80399</v>
+      </c>
+      <c r="G27" t="n">
+        <v>110592</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>广汽埃安新能源</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>13581</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>97.51%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>-82.75%</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>78724</v>
+      </c>
+      <c r="F28" t="n">
+        <v>38828</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13911</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>蔚来汽车</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>10628</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>125.74%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>-83.99%</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>66395</v>
+      </c>
+      <c r="F29" t="n">
+        <v>26375</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14257</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>小鹏汽车</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>10412</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>203.91%</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-81.54%</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>56404</v>
+      </c>
+      <c r="F30" t="n">
+        <v>13017</v>
+      </c>
+      <c r="G30" t="n">
+        <v>13602</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>江苏悦达起亚</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9307</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-64.4%</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-91.68%</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>111928</v>
+      </c>
+      <c r="F31" t="n">
+        <v>179839</v>
+      </c>
+      <c r="G31" t="n">
+        <v>215724</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>神龙汽车</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8101</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>148.12%</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>-86.9%</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>61858</v>
+      </c>
+      <c r="F32" t="n">
+        <v>32038</v>
+      </c>
+      <c r="G32" t="n">
+        <v>92707</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>东风小康</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7739</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-27.79%</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>-89.89%</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>76568</v>
+      </c>
+      <c r="F33" t="n">
+        <v>67908</v>
+      </c>
+      <c r="G33" t="n">
+        <v>119254</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>合众汽车</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7699</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>280.57%</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-81.42%</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>41427</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9246</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7029</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>理想汽车</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7094</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>102.45%</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-87.16%</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>55270</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18160</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>朋克汽车</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6959</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>695900%</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-60.07%</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>17427</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>雷丁</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6056</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>768.87%</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-67.2%</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>18461</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2828</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>广汽三菱</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5610</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-20.2%</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-87.42%</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>44582</v>
+      </c>
+      <c r="F38" t="n">
+        <v>46711</v>
+      </c>
+      <c r="G38" t="n">
+        <v>96414</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>易捷特</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5365</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7456.34%</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-16.73%</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F39" t="n">
+        <v>299</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>吉利沃尔沃</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5312</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>-61.34%</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-94.2%</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>91545</v>
+      </c>
+      <c r="F40" t="n">
+        <v>83840</v>
+      </c>
+      <c r="G40" t="n">
+        <v>86082</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>一汽奔腾</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5178</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-89.23%</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>48064</v>
+      </c>
+      <c r="F41" t="n">
+        <v>56849</v>
+      </c>
+      <c r="G41" t="n">
+        <v>74779</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>上汽大通</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5049</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>14.36%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-86.02%</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>36120</v>
+      </c>
+      <c r="F42" t="n">
+        <v>28612</v>
+      </c>
+      <c r="G42" t="n">
+        <v>40432</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>威马汽车</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5005</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>137.54%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-82.77%</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>29043</v>
+      </c>
+      <c r="F43" t="n">
+        <v>13886</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10916</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>奇瑞捷豹路虎</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4251</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>-30.02%</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-89.55%</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>40690</v>
+      </c>
+      <c r="F44" t="n">
+        <v>40717</v>
+      </c>
+      <c r="G44" t="n">
+        <v>37810</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>零跑汽车</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4095</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>290%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-85.28%</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>27817</v>
+      </c>
+      <c r="F45" t="n">
+        <v>3741</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>鑫源汽车</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4078</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>11.51%</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-86.21%</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>29582</v>
+      </c>
+      <c r="F46" t="n">
+        <v>37416</v>
+      </c>
+      <c r="G46" t="n">
+        <v>37877</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>福建奔驰</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3879</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>41.93%</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-85.21%</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>26232</v>
+      </c>
+      <c r="F47" t="n">
+        <v>19886</v>
+      </c>
+      <c r="G47" t="n">
+        <v>20752</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>江铃汽车</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3583</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>11.59%</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-84.42%</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>24331</v>
+      </c>
+      <c r="G48" t="n">
+        <v>37625</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>北京汽车</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3504</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-50.83%</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-86.06%</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>25136</v>
+      </c>
+      <c r="F49" t="n">
+        <v>40286</v>
+      </c>
+      <c r="G49" t="n">
+        <v>37170</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>北汽越野</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3076</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>33.04%</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-83.47%</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>18605</v>
+      </c>
+      <c r="F50" t="n">
+        <v>12318</v>
+      </c>
+      <c r="G50" t="n">
+        <v>15376</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>吉麦新能源</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2978</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2819.61%</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-76.65%</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>12756</v>
+      </c>
+      <c r="F51" t="n">
+        <v>102</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H1" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>上汽集团</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>623.8</v>
+      </c>
+      <c r="C2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D2" t="n">
+        <v>546.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>530.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>502.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>463.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>74</v>
+      </c>
+      <c r="E3" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>长安汽车</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>176</v>
+      </c>
+      <c r="C4" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>255.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>268</v>
+      </c>
+      <c r="H4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>广汽集团</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>206.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>204.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>长城汽车</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>106</v>
+      </c>
+      <c r="C6" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>赛力斯</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北汽蓝谷</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E1" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F1" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G1" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H1" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C2" t="n">
+        <v>43</v>
+      </c>
+      <c r="D2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>上汽集团</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>长城汽车</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>21</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>赛力斯</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>76</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93</v>
+      </c>
+      <c r="H5" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>长安汽车</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>19</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>广汽集团</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H7" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北汽蓝谷</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2023Q4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2024Q4</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>98</v>
+      </c>
+      <c r="K2" t="n">
+        <v>107</v>
+      </c>
+      <c r="L2" t="n">
+        <v>108</v>
+      </c>
+      <c r="M2" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>赛力斯</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>长安汽车</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>64</v>
+      </c>
+      <c r="M4" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上汽集团</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>122</v>
+      </c>
+      <c r="C5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" t="n">
+        <v>126</v>
+      </c>
+      <c r="F5" t="n">
+        <v>118</v>
+      </c>
+      <c r="G5" t="n">
+        <v>117</v>
+      </c>
+      <c r="H5" t="n">
+        <v>115</v>
+      </c>
+      <c r="I5" t="n">
+        <v>114</v>
+      </c>
+      <c r="J5" t="n">
+        <v>108</v>
+      </c>
+      <c r="K5" t="n">
+        <v>108</v>
+      </c>
+      <c r="L5" t="n">
+        <v>106</v>
+      </c>
+      <c r="M5" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>长城汽车</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C6" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29</v>
+      </c>
+      <c r="K6" t="n">
+        <v>33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>广汽集团</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C7" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>51</v>
+      </c>
+      <c r="G7" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北汽蓝谷</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>公司</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2025Q1同比%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025Q2同比%</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2025Q3同比%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2025Q4同比%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>比亚迪</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>赛力斯</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-7.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>长安汽车</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>上汽集团</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-7.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>长城汽车</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>广汽集团</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>江淮汽车</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>北汽蓝谷</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>赛力斯</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>长安汽车</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>差异说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>255.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>268</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>总销量</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D5" t="n">
+        <v>260</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>问界占比%</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>问界占比%</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>问界占比%</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>赛力斯集中度极高 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>问界占比%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>赛力斯集中度极高 | 长安</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>新能源占比%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安均衡发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>新能源占比%</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安均衡发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>新能源占比%</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安均衡发展</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>新能源占比%</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>赛力斯 | 长安均衡发展</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -752,7 +4285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,293 +4296,158 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>A00</t>
+          <t>2025年</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>A0</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>2026年</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-7月</t>
+          <t>1月</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13.7</v>
+        <v>74.4462</v>
       </c>
       <c r="C2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8.9</v>
+        <v>59.1814</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-8月</t>
+          <t>2月</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.9</v>
+        <v>68.3481</v>
       </c>
       <c r="C3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8</v>
+        <v>46.3209</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-9月</t>
+          <t>3月</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.8</v>
+        <v>99.1194</v>
       </c>
       <c r="C4" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E4" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8</v>
+        <v>85.17610000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10月</t>
+          <t>4月</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.2</v>
+        <v>91.1204</v>
       </c>
       <c r="C5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5.8</v>
+        <v>84.8085</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11月</t>
+          <t>5月</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.1</v>
+        <v>102.7156</v>
       </c>
       <c r="C6" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.5</v>
+        <v>95.017</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-12月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.6</v>
+        <v>111.1558</v>
       </c>
       <c r="C7" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.5</v>
+        <v>100.6753</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-1月</t>
+          <t>7月</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="C8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.7</v>
-      </c>
+        <v>98.65560000000001</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-2月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="E9" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5.6</v>
-      </c>
+        <v>111.4901</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-3月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.8</v>
-      </c>
+        <v>129.8529</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-4月</t>
+          <t>10月</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4.1</v>
-      </c>
+        <v>128.2267</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-5月</t>
+          <t>11月</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
-      </c>
-      <c r="C12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4.9</v>
-      </c>
+        <v>132.074</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-6月</t>
+          <t>12月</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3.6</v>
-      </c>
+        <v>133.6882</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1073,158 +4471,1433 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2025年</t>
+          <t>NEV</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2026年</t>
+          <t>ICE</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1月</t>
+          <t>2025-7月</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.4462</v>
+        <v>52.9</v>
       </c>
       <c r="C2" t="n">
-        <v>59.1814</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2月</t>
+          <t>2025-8月</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.3481</v>
+        <v>52.2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.3209</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3月</t>
+          <t>2025-9月</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>99.1194</v>
+        <v>53.4</v>
       </c>
       <c r="C4" t="n">
-        <v>85.17610000000001</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4月</t>
+          <t>2025-10月</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>91.1204</v>
+        <v>55</v>
       </c>
       <c r="C5" t="n">
-        <v>84.8085</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>2025-11月</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.7156</v>
+        <v>56.9</v>
       </c>
       <c r="C6" t="n">
-        <v>95.017</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6月</t>
+          <t>2025-12月</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111.1558</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
-        <v>100.6753</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7月</t>
+          <t>2026-1月</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98.65560000000001</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>43.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>56.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>2026-2月</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111.4901</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>47.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>2026-3月</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129.8529</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>48.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>51.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10月</t>
+          <t>2026-4月</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>128.2267</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C11" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11月</t>
+          <t>2026-5月</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132.074</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>61</v>
+      </c>
+      <c r="C12" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12月</t>
+          <t>2026-6月</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>133.6882</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>62.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NEV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-7月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-8月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-9月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C7" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-1月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-2月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-3月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-4月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>58</v>
+      </c>
+      <c r="C11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-5月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-6月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NEV</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-7月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-8月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-9月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>46.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>56</v>
+      </c>
+      <c r="C7" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-1月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-2月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-3月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>51.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-4月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>58</v>
+      </c>
+      <c r="C11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-5月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>61</v>
+      </c>
+      <c r="C12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-6月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>A00</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-7月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-8月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-9月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-1月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-2月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-3月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-4月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-5月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-6月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>A00</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-7月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-8月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F3" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-9月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>28</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-1月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-2月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-3月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-4月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-5月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-6月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-7月</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-8月</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>49.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-9月</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10月</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11月</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-12月</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-1月</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>44.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-2月</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-3月</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-4月</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-5月</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-6月</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
